--- a/Codelist Excel Files and Conversion Templates to XML/equipmentClass.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/equipmentClass.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="9200" yWindow="3280" windowWidth="39400" windowHeight="24940" tabRatio="500" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DictionaryName" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Definitions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="AssociatedElements" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="AlternateNames" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Lists" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DictionaryName" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AssociatedElements" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlternateNames" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1639,17 +1639,17 @@
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>displacement_auger</t>
+          <t>grout_pump</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>Displacement auger</t>
+          <t>Grout pump</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>A shaped auger that forms a rigid inclusion by displacing soil laterally rather than removing it, generating no spoil. Proprietary tool geometries in common use include APGD, Atlas, De Waal, Fundex, Olivier, Omega, SVB and SVV.</t>
+          <t>A pump delivering grout or cemented aggregate to the tool during column formation; a piston pump is typical for grouted rigid inclusions.</t>
         </is>
       </c>
       <c r="E26" s="13" t="n"/>
@@ -1663,17 +1663,17 @@
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>traction_compacting_tool</t>
+          <t>concrete_pump</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>Traction compacting tool</t>
+          <t>Concrete pump</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>A displacement tool that advances by traction and compacts soil on both insertion and extraction, typically about half on each. Offered by Keller / Hayward Baker as an alternative to a single-pass displacement auger.</t>
+          <t>A pump delivering ready-mixed concrete to the tool during column formation, typical of controlled-modulus-column practice.</t>
         </is>
       </c>
       <c r="E27" s="13" t="n"/>
@@ -1687,22 +1687,30 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>vibratory_displacement_tool</t>
+          <t>rapid_load_device</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>Vibratory displacement tool</t>
+          <t>Rapid Load Test Device</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>A displacement tool advanced by vibration rather than by rotary drilling or static push.</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="n"/>
+          <t>The pneumatic or hydraulic force-pulse generator used to apply the load in a rapid load test - a Statnamic device or an equivalent force-pulse actuator, per ASTM D7383 or EN ISO 22477-10.</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="F28" s="13" t="n"/>
-      <c r="G28" s="9" t="n"/>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2">
@@ -1711,22 +1719,30 @@
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>grout_pump</t>
+          <t>dynamic_test_hammer</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>Grout pump</t>
+          <t>Dynamic Load Test Hammer</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>A pump delivering grout or cemented aggregate to the tool during column formation; a piston pump is typical for grouted rigid inclusions.</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="n"/>
+          <t>The impact hammer used to apply the blow(s) in a high-strain dynamic load test, per ASTM D4945 or EN ISO 22477-4.</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="F29" s="13" t="n"/>
-      <c r="G29" s="9" t="n"/>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2">
@@ -1735,22 +1751,30 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>concrete_pump</t>
+          <t>low_strain_impact_hammer</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>Concrete pump</t>
+          <t>Low-Strain Impact Hammer</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>A pump delivering ready-mixed concrete to the tool during column formation, typical of controlled-modulus-column practice.</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="n"/>
+          <t>The small handheld hammer (typically plastic- or rubber-tipped) used to apply the impact in a low-strain integrity test, per ASTM D5882 or NF P94-160-2/-4. Distinct from equipmentClass.xml#dynamic_test_hammer, the much larger drop or diesel hammer used to apply a high-strain blow in ASTM D4945 dynamic load testing - the two tests use different equipment at entirely different energy scales.</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="F30" s="13" t="n"/>
-      <c r="G30" s="9" t="n"/>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2">
@@ -1759,17 +1783,17 @@
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>rapid_load_device</t>
+          <t>thermal_integrity_probe</t>
         </is>
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>Rapid Load Test Device</t>
+          <t>Thermal Integrity Profiling Probe</t>
         </is>
       </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
-          <t>The pneumatic or hydraulic force-pulse generator used to apply the load in a rapid load test - a Statnamic device or an equivalent force-pulse actuator, per ASTM D7383 or EN ISO 22477-10.</t>
+          <t>The probe lowered into access ducts to take temperature readings in ASTM D7949 Method A thermal integrity profiling. Distinct from equipmentClass.xml#thermistor, which is the embedded sensor Method B uses instead - the two methods use different equipment classes for the same underlying measurement.</t>
         </is>
       </c>
       <c r="E31" s="18" t="inlineStr">
@@ -1791,17 +1815,17 @@
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>dynamic_test_hammer</t>
+          <t>embedded_fiber_optic_cable</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>Dynamic Load Test Hammer</t>
+          <t>Embedded Fiber-Optic Cable</t>
         </is>
       </c>
       <c r="D32" s="19" t="inlineStr">
         <is>
-          <t>The impact hammer used to apply the blow(s) in a high-strain dynamic load test, per ASTM D4945 or EN ISO 22477-4.</t>
+          <t>The fiber-optic cable attached to the reinforcing cage and cast into the concrete for ASTM D7949 Method C thermal integrity profiling, giving effectively continuous temperature coverage along the element's length.</t>
         </is>
       </c>
       <c r="E32" s="18" t="inlineStr">
@@ -1821,96 +1845,36 @@
         <f>IF(ISNA(VLOOKUP(B33,AssociatedElements!B$2:B2971,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>low_strain_impact_hammer</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="inlineStr">
-        <is>
-          <t>Low-Strain Impact Hammer</t>
-        </is>
-      </c>
-      <c r="D33" s="19" t="inlineStr">
-        <is>
-          <t>The small handheld hammer (typically plastic- or rubber-tipped) used to apply the impact in a low-strain integrity test, per ASTM D5882 or NF P94-160-2/-4. Distinct from equipmentClass.xml#dynamic_test_hammer, the much larger drop or diesel hammer used to apply a high-strain blow in ASTM D4945 dynamic load testing - the two tests use different equipment at entirely different energy scales.</t>
-        </is>
-      </c>
-      <c r="E33" s="18" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
+      <c r="B33" s="13" t="n"/>
+      <c r="C33" s="18" t="n"/>
+      <c r="D33" s="19" t="n"/>
+      <c r="E33" s="18" t="n"/>
       <c r="F33" s="18" t="n"/>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>DIGGS</t>
-        </is>
-      </c>
+      <c r="G33" s="9" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2">
         <f>IF(ISNA(VLOOKUP(B34,AssociatedElements!B$2:B2972,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="B34" s="13" t="inlineStr">
-        <is>
-          <t>thermal_integrity_probe</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>Thermal Integrity Profiling Probe</t>
-        </is>
-      </c>
-      <c r="D34" s="19" t="inlineStr">
-        <is>
-          <t>The probe lowered into access ducts to take temperature readings in ASTM D7949 Method A thermal integrity profiling. Distinct from equipmentClass.xml#thermistor, which is the embedded sensor Method B uses instead - the two methods use different equipment classes for the same underlying measurement.</t>
-        </is>
-      </c>
-      <c r="E34" s="18" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
+      <c r="B34" s="13" t="n"/>
+      <c r="C34" s="18" t="n"/>
+      <c r="D34" s="19" t="n"/>
+      <c r="E34" s="18" t="n"/>
       <c r="F34" s="18" t="n"/>
-      <c r="G34" s="9" t="inlineStr">
-        <is>
-          <t>DIGGS</t>
-        </is>
-      </c>
+      <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2">
         <f>IF(ISNA(VLOOKUP(B35,AssociatedElements!B$2:B2973,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="B35" s="13" t="inlineStr">
-        <is>
-          <t>embedded_fiber_optic_cable</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="inlineStr">
-        <is>
-          <t>Embedded Fiber-Optic Cable</t>
-        </is>
-      </c>
-      <c r="D35" s="19" t="inlineStr">
-        <is>
-          <t>The fiber-optic cable attached to the reinforcing cage and cast into the concrete for ASTM D7949 Method C thermal integrity profiling, giving effectively continuous temperature coverage along the element's length.</t>
-        </is>
-      </c>
-      <c r="E35" s="18" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
+      <c r="B35" s="13" t="n"/>
+      <c r="C35" s="18" t="n"/>
+      <c r="D35" s="19" t="n"/>
+      <c r="E35" s="18" t="n"/>
       <c r="F35" s="18" t="n"/>
-      <c r="G35" s="9" t="inlineStr">
-        <is>
-          <t>DIGGS</t>
-        </is>
-      </c>
+      <c r="G35" s="9" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2">
@@ -2368,7 +2332,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>displacement_auger</t>
+          <t>grout_pump</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2384,7 +2348,7 @@
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>traction_compacting_tool</t>
+          <t>concrete_pump</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2400,7 +2364,7 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>vibratory_displacement_tool</t>
+          <t>rapid_load_device</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2416,7 +2380,7 @@
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>grout_pump</t>
+          <t>dynamic_test_hammer</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2432,7 +2396,7 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>concrete_pump</t>
+          <t>low_strain_impact_hammer</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2448,7 +2412,7 @@
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>rapid_load_device</t>
+          <t>thermal_integrity_probe</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2464,7 +2428,7 @@
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>dynamic_test_hammer</t>
+          <t>embedded_fiber_optic_cable</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2478,48 +2442,21 @@
         <f>IF(ISNA(VLOOKUP(B33,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>low_strain_impact_hammer</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>//diggs:Equipment/diggs:class</t>
-        </is>
-      </c>
+      <c r="B33" s="13" t="n"/>
     </row>
     <row r="34">
       <c r="A34">
         <f>IF(ISNA(VLOOKUP(B34,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B34" s="13" t="inlineStr">
-        <is>
-          <t>thermal_integrity_probe</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>//diggs:Equipment/diggs:class</t>
-        </is>
-      </c>
+      <c r="B34" s="13" t="n"/>
     </row>
     <row r="35">
       <c r="A35">
         <f>IF(ISNA(VLOOKUP(B35,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B35" s="13" t="inlineStr">
-        <is>
-          <t>embedded_fiber_optic_cable</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>//diggs:Equipment/diggs:class</t>
-        </is>
-      </c>
+      <c r="B35" s="13" t="n"/>
     </row>
     <row r="36">
       <c r="A36">

--- a/Codelist Excel Files and Conversion Templates to XML/equipmentClass.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/equipmentClass.xlsx
@@ -1845,9 +1845,21 @@
         <f>IF(ISNA(VLOOKUP(B33,AssociatedElements!B$2:B2971,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="18" t="n"/>
-      <c r="D33" s="19" t="n"/>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>dial_gauge</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>Dial gauge</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>A mechanical or digital indicator that reads a displacement directly, mounted on a reference beam to measure the settlement of a test plate or pile head.</t>
+        </is>
+      </c>
       <c r="E33" s="18" t="n"/>
       <c r="F33" s="18" t="n"/>
       <c r="G33" s="9" t="n"/>
@@ -1857,9 +1869,21 @@
         <f>IF(ISNA(VLOOKUP(B34,AssociatedElements!B$2:B2972,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="B34" s="13" t="n"/>
-      <c r="C34" s="18" t="n"/>
-      <c r="D34" s="19" t="n"/>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>pressure_gauge</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>Pressure gauge</t>
+        </is>
+      </c>
+      <c r="D34" s="19" t="inlineStr">
+        <is>
+          <t>A gauge that reads fluid pressure, for example the Bourdon-tube gauge on a hydraulic jack that gives the load applied in a static load test.</t>
+        </is>
+      </c>
       <c r="E34" s="18" t="n"/>
       <c r="F34" s="18" t="n"/>
       <c r="G34" s="9" t="n"/>
@@ -2442,14 +2466,32 @@
         <f>IF(ISNA(VLOOKUP(B33,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B33" s="13" t="n"/>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>dial_gauge</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>//diggs:Equipment/diggs:class</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
         <f>IF(ISNA(VLOOKUP(B34,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B34" s="13" t="n"/>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>pressure_gauge</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>//diggs:Equipment/diggs:class</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35">

--- a/Codelist Excel Files and Conversion Templates to XML/equipmentClass.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/equipmentClass.xlsx
@@ -2498,7 +2498,16 @@
         <f>IF(ISNA(VLOOKUP(B35,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B35" s="13" t="n"/>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>accelerometer</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>//diggs:Equipment/diggs:class</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
